--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.6270470619935</v>
+        <v>9.526895147573944</v>
       </c>
       <c r="D2" t="n">
-        <v>21.84124988429338</v>
+        <v>3.549203106197674</v>
       </c>
       <c r="E2" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F2" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.33361039026719</v>
+        <v>8.341711688418419</v>
       </c>
       <c r="D3" t="n">
-        <v>17.44276354251241</v>
+        <v>2.834449075658267</v>
       </c>
       <c r="E3" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F3" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.58115783198142</v>
+        <v>7.731938147696981</v>
       </c>
       <c r="D4" t="n">
-        <v>38.16084380618437</v>
+        <v>6.20113711850496</v>
       </c>
       <c r="E4" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F4" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.44220459057232</v>
+        <v>4.296858245968003</v>
       </c>
       <c r="D5" t="n">
-        <v>26.67324475213449</v>
+        <v>4.334402272221854</v>
       </c>
       <c r="E5" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F5" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.47009766571428</v>
+        <v>8.201390870678571</v>
       </c>
       <c r="D6" t="n">
-        <v>43.80433386860125</v>
+        <v>7.118204253647704</v>
       </c>
       <c r="E6" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F6" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.91261376452551</v>
+        <v>5.835799736735396</v>
       </c>
       <c r="D7" t="n">
-        <v>30.22544187965155</v>
+        <v>4.911634305443377</v>
       </c>
       <c r="E7" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F7" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.388337360767339</v>
+        <v>1.363104821124693</v>
       </c>
       <c r="D8" t="n">
-        <v>7.714564128497941</v>
+        <v>1.253616670880916</v>
       </c>
       <c r="E8" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F8" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.04634823888765</v>
+        <v>5.207531588819243</v>
       </c>
       <c r="D9" t="n">
-        <v>37.10169900118893</v>
+        <v>6.029026087693201</v>
       </c>
       <c r="E9" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F9" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.79823215565449</v>
+        <v>2.729712725293854</v>
       </c>
       <c r="D10" t="n">
-        <v>10.54383511959103</v>
+        <v>1.713373206933543</v>
       </c>
       <c r="E10" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F10" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.29125151567677</v>
+        <v>2.809828371297475</v>
       </c>
       <c r="D11" t="n">
-        <v>23.71298506229939</v>
+        <v>3.853360072623651</v>
       </c>
       <c r="E11" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F11" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.89907055210258</v>
+        <v>5.833598964716669</v>
       </c>
       <c r="D12" t="n">
-        <v>30.14807717686409</v>
+        <v>4.899062541240415</v>
       </c>
       <c r="E12" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F12" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.07005859733223</v>
+        <v>5.861384522066487</v>
       </c>
       <c r="D13" t="n">
-        <v>42.6924897514015</v>
+        <v>6.937529584602744</v>
       </c>
       <c r="E13" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F13" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.07671033488461</v>
+        <v>7.649965429418749</v>
       </c>
       <c r="D14" t="n">
-        <v>46.94608760687355</v>
+        <v>7.628739236116951</v>
       </c>
       <c r="E14" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F14" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.35335407037897</v>
+        <v>3.307420036436583</v>
       </c>
       <c r="D15" t="n">
-        <v>26.84144995644594</v>
+        <v>4.361735617922466</v>
       </c>
       <c r="E15" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F15" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.77098107252804</v>
+        <v>5.000284424285807</v>
       </c>
       <c r="D16" t="n">
-        <v>26.80778397945806</v>
+        <v>4.356264896661935</v>
       </c>
       <c r="E16" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F16" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.52447454819057</v>
+        <v>7.235227114080968</v>
       </c>
       <c r="D17" t="n">
-        <v>44.00997397504074</v>
+        <v>7.151620770944121</v>
       </c>
       <c r="E17" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F17" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.29994548724546</v>
+        <v>4.761241141677386</v>
       </c>
       <c r="D18" t="n">
-        <v>40.24549100535135</v>
+        <v>6.539892288369594</v>
       </c>
       <c r="E18" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F18" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.34166586553867</v>
+        <v>7.043020703150034</v>
       </c>
       <c r="D19" t="n">
-        <v>77.27893000408473</v>
+        <v>12.55782612566377</v>
       </c>
       <c r="E19" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F19" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>11.20182737109065</v>
+        <v>1.820296947802231</v>
       </c>
       <c r="D20" t="n">
-        <v>11.52397579387098</v>
+        <v>1.872646066504035</v>
       </c>
       <c r="E20" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F20" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13.64463777278982</v>
+        <v>2.217253638078346</v>
       </c>
       <c r="D21" t="n">
-        <v>13.15697775931464</v>
+        <v>2.138008885888629</v>
       </c>
       <c r="E21" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F21" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>2.20961981352809</v>
+        <v>0.3590632196983147</v>
       </c>
       <c r="D22" t="n">
-        <v>2.14445747633783</v>
+        <v>0.3484743399048974</v>
       </c>
       <c r="E22" t="n">
-        <v>15.51669171298549</v>
+        <v>2.521462403360142</v>
       </c>
       <c r="F22" t="n">
-        <v>16.70174260551144</v>
+        <v>2.714033173395609</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
